--- a/data/planilhas/CT_317_NORMALIZADA.xlsx
+++ b/data/planilhas/CT_317_NORMALIZADA.xlsx
@@ -4478,7 +4478,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-03T09:33:57.786886</t>
+          <t>2026-06-11T23:24:47.381187</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/planilhas/CT_317_NORMALIZADA.xlsx
+++ b/data/planilhas/CT_317_NORMALIZADA.xlsx
@@ -4478,7 +4478,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-11T23:24:47.381187</t>
+          <t>2026-06-15T11:06:26.133627</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
